--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119543003</v>
+        <v>119542725</v>
       </c>
       <c r="B15" t="n">
-        <v>105009</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518405</v>
+        <v>518360</v>
       </c>
       <c r="R15" t="n">
-        <v>6719008</v>
+        <v>6719065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119542725</v>
+        <v>119543003</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>105009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2488,25 +2488,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518360</v>
+        <v>518405</v>
       </c>
       <c r="R16" t="n">
-        <v>6719065</v>
+        <v>6719008</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119542725</v>
+        <v>119543003</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>105009</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518360</v>
+        <v>518405</v>
       </c>
       <c r="R15" t="n">
-        <v>6719065</v>
+        <v>6719008</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119543003</v>
+        <v>119542725</v>
       </c>
       <c r="B16" t="n">
-        <v>105009</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2488,25 +2488,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518405</v>
+        <v>518360</v>
       </c>
       <c r="R16" t="n">
-        <v>6719008</v>
+        <v>6719065</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,6 +2586,132 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126571260</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>518385</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6719014</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Över ca 2kv/m</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>126571260</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>126571260</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2712,1277 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128343039</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>518329</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6719026</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128343148</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>518345</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6719051</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128342890</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>518297</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6719118</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128343222</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>518355</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6719034</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128342810</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>518323</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6719165</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128343196</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>518358</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719040</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128343284</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>518348</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6719026</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128342618</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>518419</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6719030</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 30.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128342638</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>518383</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6719076</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128343538</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90859</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>518357</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mellan gran och tall, mossmatta.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128343024</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>518332</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6719027</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -3403,7 +3403,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128343284</v>
+        <v>128342618</v>
       </c>
       <c r="B24" t="n">
         <v>98473</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518348</v>
+        <v>518419</v>
       </c>
       <c r="R24" t="n">
-        <v>6719026</v>
+        <v>6719030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3497,7 +3497,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 30.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3524,7 +3529,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342618</v>
+        <v>128343284</v>
       </c>
       <c r="B25" t="n">
         <v>98473</v>
@@ -3554,7 +3559,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518419</v>
+        <v>518348</v>
       </c>
       <c r="R25" t="n">
-        <v>6719030</v>
+        <v>6719026</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3618,12 +3623,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 30.</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3054,59 +3054,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98473</v>
+        <v>92673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3124,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3148,7 +3134,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,45 +3161,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92673</v>
+        <v>98473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3983,6 +3983,668 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128394929</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>518349</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6719016</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128394409</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105514</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>518388</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6718995</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128395367</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>518320</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6719051</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128395455</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>518317</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6719077</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128395336</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>518324</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6719062</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128394612</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91990</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>518364</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6719016</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lite osäker men vet inte annars vad.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,48 +3762,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128343538</v>
+        <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>90859</v>
+        <v>92673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>256703</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518357</v>
+        <v>518332</v>
       </c>
       <c r="R27" t="n">
-        <v>6719013</v>
+        <v>6719027</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3835,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3845,12 +3842,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mellan gran och tall, mossmatta.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3859,7 +3851,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3878,10 +3869,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128343024</v>
+        <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>92673</v>
+        <v>57833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3889,34 +3880,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518332</v>
+        <v>518349</v>
       </c>
       <c r="R28" t="n">
-        <v>6719027</v>
+        <v>6719016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3943,22 +3939,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3985,50 +3981,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128394929</v>
+        <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>57833</v>
+        <v>105514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518349</v>
+        <v>518388</v>
       </c>
       <c r="R29" t="n">
-        <v>6719016</v>
+        <v>6718995</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4060,7 +4051,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4070,7 +4061,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4097,10 +4088,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128394409</v>
+        <v>128395367</v>
       </c>
       <c r="B30" t="n">
-        <v>105514</v>
+        <v>4773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4108,37 +4099,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518388</v>
+        <v>518320</v>
       </c>
       <c r="R30" t="n">
-        <v>6718995</v>
+        <v>6719051</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4167,7 +4163,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4177,7 +4173,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4192,22 +4188,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Karl Ericson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128395367</v>
+        <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>4773</v>
+        <v>92648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4215,42 +4211,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518320</v>
+        <v>518317</v>
       </c>
       <c r="R31" t="n">
-        <v>6719051</v>
+        <v>6719077</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,7 +4270,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4289,7 +4280,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4304,22 +4295,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128395455</v>
+        <v>128395336</v>
       </c>
       <c r="B32" t="n">
-        <v>92648</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,34 +4318,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518317</v>
+        <v>518324</v>
       </c>
       <c r="R32" t="n">
-        <v>6719077</v>
+        <v>6719062</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4386,7 +4382,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4396,7 +4392,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4423,10 +4419,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128395336</v>
+        <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>91990</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4434,39 +4430,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518324</v>
+        <v>518364</v>
       </c>
       <c r="R33" t="n">
-        <v>6719062</v>
+        <v>6719016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4498,7 +4489,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4508,7 +4499,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lite osäker men vet inte annars vad.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4535,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128394612</v>
+        <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>91990</v>
+        <v>90862</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4546,34 +4542,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6031</v>
+        <v>256703</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518364</v>
+        <v>518348</v>
       </c>
       <c r="R34" t="n">
-        <v>6719016</v>
+        <v>6719024</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4600,27 +4599,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lite osäker men vet inte annars vad.</t>
+          <t>Bland gran och tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4629,6 +4628,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4644,6 +4644,233 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128394906</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90862</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>518339</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6719046</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128343538</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90862</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>518357</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mellan gran och tall, mossmatta.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,45 +2714,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B18" t="n">
-        <v>92673</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R18" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2784,7 +2798,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2794,7 +2808,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2821,59 +2835,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B19" t="n">
-        <v>98473</v>
+        <v>92678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R19" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2945,7 +2945,7 @@
         <v>128342890</v>
       </c>
       <c r="B20" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3054,45 +3054,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>92673</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3124,7 +3138,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3134,7 +3148,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3161,59 +3175,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>98473</v>
+        <v>92678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92673</v>
+        <v>92678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105514</v>
+        <v>105516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>91990</v>
+        <v>91992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343148</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128343039</v>
       </c>
       <c r="B19" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128342890</v>
       </c>
       <c r="B20" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,59 +2714,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>92770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R18" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2798,7 +2784,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2808,7 +2794,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,45 +2821,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>92770</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R19" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3054,59 +3054,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>92770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3124,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3148,7 +3134,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,45 +3161,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92770</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -3054,45 +3054,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>92770</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3124,7 +3138,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3134,7 +3148,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3161,59 +3175,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>92770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128342890</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92084</v>
+        <v>92096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90954</v>
+        <v>90966</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90954</v>
+        <v>90966</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,59 +3054,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3124,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3148,7 +3134,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,45 +3161,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92782</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,45 +2714,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R18" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2784,7 +2798,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2794,7 +2808,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2821,59 +2835,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R19" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3164,7 +3164,7 @@
         <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,59 +2714,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>92785</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R18" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2798,7 +2784,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2808,7 +2794,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,45 +2821,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R19" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3057,7 +3057,7 @@
         <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -3054,45 +3054,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>92785</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3124,7 +3138,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3134,7 +3148,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3161,59 +3175,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>92785</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128342890</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3054,59 +3054,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>92812</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3124,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3148,7 +3134,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,45 +3161,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92785</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,7 +3285,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -3054,45 +3054,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>92812</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3124,7 +3138,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3134,7 +3148,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3161,59 +3175,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>92812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4761,7 +4761,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,21 +2727,12 @@
       <c r="E18" t="n">
         <v>5449</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2824,7 +2815,7 @@
         <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,59 +3045,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>92823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3106,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3148,7 +3116,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,45 +3143,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92812</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,7 +3267,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3388,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3532,7 +3514,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,7 +3635,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3747,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3775,21 +3757,12 @@
       <c r="E27" t="n">
         <v>5449</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3984,7 +3957,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105682</v>
+        <v>105695</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4203,7 +4176,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,7 +4395,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92126</v>
+        <v>92136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4534,7 +4507,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>90996</v>
+        <v>91006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,7 +4623,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>90996</v>
+        <v>91006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4734,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,36 +2714,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R18" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2775,7 +2798,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2785,7 +2808,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2812,59 +2835,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R19" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3385,7 +3385,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342618</v>
+        <v>128343284</v>
       </c>
       <c r="B24" t="n">
         <v>98632</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518419</v>
+        <v>518348</v>
       </c>
       <c r="R24" t="n">
-        <v>6719030</v>
+        <v>6719026</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3479,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 30.</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3511,7 +3506,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128343284</v>
+        <v>128342618</v>
       </c>
       <c r="B25" t="n">
         <v>98632</v>
@@ -3541,7 +3536,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3560,10 +3555,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518348</v>
+        <v>518419</v>
       </c>
       <c r="R25" t="n">
-        <v>6719026</v>
+        <v>6719030</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3595,7 +3590,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3605,7 +3600,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 30.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2714,59 +2714,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343148</v>
+        <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518345</v>
+        <v>518329</v>
       </c>
       <c r="R18" t="n">
-        <v>6719051</v>
+        <v>6719026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2798,7 +2775,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2808,7 +2785,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,36 +2812,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343039</v>
+        <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518329</v>
+        <v>518345</v>
       </c>
       <c r="R19" t="n">
-        <v>6719026</v>
+        <v>6719051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3045,36 +3045,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B21" t="n">
-        <v>92823</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3106,7 +3129,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3116,7 +3139,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3143,59 +3166,36 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>92823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3385,7 +3385,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128343284</v>
+        <v>128342618</v>
       </c>
       <c r="B24" t="n">
         <v>98632</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518348</v>
+        <v>518419</v>
       </c>
       <c r="R24" t="n">
-        <v>6719026</v>
+        <v>6719030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,7 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 30.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3506,7 +3511,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342618</v>
+        <v>128343284</v>
       </c>
       <c r="B25" t="n">
         <v>98632</v>
@@ -3536,7 +3541,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3555,10 +3560,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518419</v>
+        <v>518348</v>
       </c>
       <c r="R25" t="n">
-        <v>6719030</v>
+        <v>6719026</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3590,7 +3595,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3600,12 +3605,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 30.</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Bo karlstens, Karl Ericson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Bo karlstens, Karl Ericson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2717,7 +2717,7 @@
         <v>128343039</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>128343148</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>128342890</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3045,59 +3045,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343222</v>
+        <v>128342810</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>92827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518355</v>
+        <v>518323</v>
       </c>
       <c r="R21" t="n">
-        <v>6719034</v>
+        <v>6719165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3129,7 +3106,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3139,7 +3116,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3166,36 +3143,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342810</v>
+        <v>128343222</v>
       </c>
       <c r="B22" t="n">
-        <v>92823</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518323</v>
+        <v>518355</v>
       </c>
       <c r="R22" t="n">
-        <v>6719165</v>
+        <v>6719034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3267,7 +3267,7 @@
         <v>128343196</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128342618</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>128343284</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>128342638</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128343024</v>
       </c>
       <c r="B27" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Bo karlstens, Karl Ericson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens, Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4845,6 +4845,200 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128999291</v>
+      </c>
+      <c r="B37" t="n">
+        <v>86939</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>518384</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6719010</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128999109</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92797</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum fennicum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>518364</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6718999</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>128394929</v>
       </c>
       <c r="B28" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>128394409</v>
       </c>
       <c r="B29" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128395455</v>
       </c>
       <c r="B31" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128394612</v>
       </c>
       <c r="B33" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128343355</v>
       </c>
       <c r="B34" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>128394906</v>
       </c>
       <c r="B35" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>128343538</v>
       </c>
       <c r="B36" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92815</v>
+        <v>92818</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92832</v>
+        <v>92834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86970</v>
+        <v>86971</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92834</v>
+        <v>92820</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86971</v>
+        <v>86974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86974</v>
+        <v>86976</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92824</v>
+        <v>92826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92826</v>
+        <v>92830</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>128999291</v>
       </c>
       <c r="B37" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92830</v>
+        <v>92831</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -4947,7 +4947,7 @@
         <v>128999109</v>
       </c>
       <c r="B38" t="n">
-        <v>92831</v>
+        <v>92834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>126571260</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5039,6 +5039,470 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130819233</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92234</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>518364</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6719063</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130819210</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91775</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>518385</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6719051</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130819189</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92194</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>518368</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6719049</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130819196</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92073</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>658</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Finnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>518374</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6719039</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -5044,7 +5044,7 @@
         <v>130819233</v>
       </c>
       <c r="B39" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>130819210</v>
       </c>
       <c r="B40" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>130819189</v>
       </c>
       <c r="B41" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>130819196</v>
       </c>
       <c r="B42" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119392138</v>
+        <v>130819196</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnhyttan, Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518435</v>
+        <v>518374</v>
       </c>
       <c r="R2" t="n">
-        <v>6719020</v>
+        <v>6719039</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19:25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>19:25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,85 +757,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119392025</v>
+        <v>119542725</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518424</v>
+        <v>518360</v>
       </c>
       <c r="R3" t="n">
-        <v>6719053</v>
+        <v>6719065</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,27 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:54</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rosetter inom 0.5 kvm</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,84 +886,63 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119391159</v>
+        <v>130819210</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnhyttan, Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518365</v>
+        <v>518385</v>
       </c>
       <c r="R4" t="n">
-        <v>6719025</v>
+        <v>6719051</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,27 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:32</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera som vart i blom och större yta med rosetter i mossan</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,90 +980,85 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119391322</v>
+        <v>130819233</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnhyttan, Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518380</v>
+        <v>518364</v>
       </c>
       <c r="R5" t="n">
-        <v>6719021</v>
+        <v>6719063</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:41</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:41</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,90 +1096,82 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119391463</v>
+        <v>128999109</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnhyttan, Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518351</v>
+        <v>518364</v>
       </c>
       <c r="R6" t="n">
-        <v>6719058</v>
+        <v>6718999</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,22 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:46</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:46</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,84 +1215,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119391503</v>
+        <v>128999291</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnhyttan, Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518344</v>
+        <v>518384</v>
       </c>
       <c r="R7" t="n">
-        <v>6719038</v>
+        <v>6719010</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1419,22 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,79 +1312,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119392358</v>
+        <v>128395455</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518394</v>
+        <v>518317</v>
       </c>
       <c r="R8" t="n">
-        <v>6718981</v>
+        <v>6719077</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,22 +1389,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1580,74 +1424,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119392079</v>
+        <v>128394612</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518420</v>
+        <v>518364</v>
       </c>
       <c r="R9" t="n">
-        <v>6719063</v>
+        <v>6719016</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,22 +1496,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lite osäker men vet inte annars vad.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,59 +1536,45 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119392415</v>
+        <v>119391555</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1767,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518401</v>
+        <v>518334</v>
       </c>
       <c r="R10" t="n">
-        <v>6718987</v>
+        <v>6719041</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1802,7 +1618,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1812,12 +1628,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 10st</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,57 +1655,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119391582</v>
+        <v>128395367</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1903,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518360</v>
+        <v>518320</v>
       </c>
       <c r="R11" t="n">
-        <v>6719065</v>
+        <v>6719051</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1933,27 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kvm</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1968,55 +1755,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119391555</v>
+        <v>128395336</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2025,13 +1807,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518334</v>
+        <v>518324</v>
       </c>
       <c r="R12" t="n">
-        <v>6719041</v>
+        <v>6719062</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2055,22 +1837,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2097,57 +1879,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119391285</v>
+        <v>128342890</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2156,13 +1919,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518361</v>
+        <v>518297</v>
       </c>
       <c r="R13" t="n">
-        <v>6719013</v>
+        <v>6719118</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2186,22 +1949,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,57 +1991,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119391190</v>
+        <v>128394929</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2287,13 +2031,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518363</v>
+        <v>518349</v>
       </c>
       <c r="R14" t="n">
-        <v>6719024</v>
+        <v>6719016</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2317,27 +2061,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 stängsel och fler rosetter</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2364,53 +2103,67 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119543003</v>
+        <v>119391159</v>
       </c>
       <c r="B15" t="n">
-        <v>105009</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518405</v>
+        <v>518365</v>
       </c>
       <c r="R15" t="n">
-        <v>6719008</v>
+        <v>6719025</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2434,22 +2187,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera som vart i blom och större yta med rosetter i mossan</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2464,65 +2222,79 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119542725</v>
+        <v>119391190</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518360</v>
+        <v>518363</v>
       </c>
       <c r="R16" t="n">
-        <v>6719065</v>
+        <v>6719024</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2546,22 +2318,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 stängsel och fler rosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,22 +2353,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126571260</v>
+        <v>119391285</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2618,7 +2395,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2628,7 +2405,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2637,13 +2419,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518385</v>
+        <v>518361</v>
       </c>
       <c r="R17" t="n">
-        <v>6719014</v>
+        <v>6719013</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2667,27 +2449,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:43</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Över ca 2kv/m</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,39 +2491,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343039</v>
+        <v>119391322</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518329</v>
+        <v>518380</v>
       </c>
       <c r="R18" t="n">
-        <v>6719026</v>
+        <v>6719021</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2770,7 +2575,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2780,7 +2585,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2812,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343148</v>
+        <v>119391463</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2842,7 +2647,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2855,19 +2660,24 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518345</v>
+        <v>518351</v>
       </c>
       <c r="R19" t="n">
-        <v>6719051</v>
+        <v>6719058</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,22 +2701,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2933,38 +2743,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128342890</v>
+        <v>119391503</v>
       </c>
       <c r="B20" t="n">
-        <v>57880</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2973,13 +2797,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518297</v>
+        <v>518344</v>
       </c>
       <c r="R20" t="n">
-        <v>6719118</v>
+        <v>6719038</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3003,22 +2827,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3045,39 +2869,67 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342810</v>
+        <v>119391582</v>
       </c>
       <c r="B21" t="n">
-        <v>92827</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518323</v>
+        <v>518360</v>
       </c>
       <c r="R21" t="n">
-        <v>6719165</v>
+        <v>6719065</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3101,22 +2953,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3143,10 +3000,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343222</v>
+        <v>119392025</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,17 +3030,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3192,13 +3049,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518355</v>
+        <v>518424</v>
       </c>
       <c r="R22" t="n">
-        <v>6719034</v>
+        <v>6719053</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3222,22 +3079,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rosetter inom 0.5 kvm</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3264,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128343196</v>
+        <v>119392079</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3294,17 +3156,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3313,13 +3175,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518358</v>
+        <v>518420</v>
       </c>
       <c r="R23" t="n">
-        <v>6719040</v>
+        <v>6719063</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3343,22 +3205,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3385,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342618</v>
+        <v>119392138</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,17 +3277,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3434,13 +3296,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518419</v>
+        <v>518435</v>
       </c>
       <c r="R24" t="n">
-        <v>6719030</v>
+        <v>6719020</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3464,27 +3326,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 30.</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3511,10 +3368,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128343284</v>
+        <v>119392358</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,17 +3398,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3560,13 +3417,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518348</v>
+        <v>518394</v>
       </c>
       <c r="R25" t="n">
-        <v>6719026</v>
+        <v>6718981</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3590,22 +3447,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3632,10 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342638</v>
+        <v>119392415</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,10 +3517,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3672,13 +3538,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518383</v>
+        <v>518401</v>
       </c>
       <c r="R26" t="n">
-        <v>6719076</v>
+        <v>6718987</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3702,22 +3568,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3744,36 +3615,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128343024</v>
+        <v>126571260</v>
       </c>
       <c r="B27" t="n">
-        <v>92827</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518332</v>
+        <v>518385</v>
       </c>
       <c r="R27" t="n">
-        <v>6719027</v>
+        <v>6719014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3800,22 +3694,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Över ca 2kv/m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,38 +3741,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128394929</v>
+        <v>128342618</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3882,10 +3790,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518349</v>
+        <v>518419</v>
       </c>
       <c r="R28" t="n">
-        <v>6719016</v>
+        <v>6719030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3912,22 +3820,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 30.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3954,45 +3867,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128394409</v>
+        <v>128342638</v>
       </c>
       <c r="B29" t="n">
-        <v>105706</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518388</v>
+        <v>518383</v>
       </c>
       <c r="R29" t="n">
-        <v>6718995</v>
+        <v>6719076</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4019,22 +3937,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,38 +3979,47 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128395367</v>
+        <v>128343148</v>
       </c>
       <c r="B30" t="n">
-        <v>4773</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4101,13 +4028,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518320</v>
+        <v>518345</v>
       </c>
       <c r="R30" t="n">
         <v>6719051</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4131,22 +4058,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4161,57 +4088,71 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128395455</v>
+        <v>128343196</v>
       </c>
       <c r="B31" t="n">
-        <v>92803</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518317</v>
+        <v>518358</v>
       </c>
       <c r="R31" t="n">
-        <v>6719077</v>
+        <v>6719040</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4238,22 +4179,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4273,45 +4214,54 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128395336</v>
+        <v>128343222</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4320,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518324</v>
+        <v>518355</v>
       </c>
       <c r="R32" t="n">
-        <v>6719062</v>
+        <v>6719034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4350,22 +4300,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4392,45 +4342,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128394612</v>
+        <v>128343284</v>
       </c>
       <c r="B33" t="n">
-        <v>92145</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518364</v>
+        <v>518348</v>
       </c>
       <c r="R33" t="n">
-        <v>6719016</v>
+        <v>6719026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4457,27 +4421,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Lite osäker men vet inte annars vad.</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4497,17 +4456,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128343355</v>
+        <v>119543003</v>
       </c>
       <c r="B34" t="n">
-        <v>91017</v>
+        <v>106244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4515,40 +4474,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256703</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518348</v>
+        <v>518405</v>
       </c>
       <c r="R34" t="n">
-        <v>6719024</v>
+        <v>6719008</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4572,27 +4528,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bland gran och tall.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4601,29 +4552,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128394906</v>
+        <v>128394409</v>
       </c>
       <c r="B35" t="n">
-        <v>91017</v>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,40 +4581,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256703</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518339</v>
+        <v>518388</v>
       </c>
       <c r="R35" t="n">
-        <v>6719046</v>
+        <v>6718995</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4693,7 +4640,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4703,7 +4650,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4712,33 +4659,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343538</v>
+        <v>128343355</v>
       </c>
       <c r="B36" t="n">
-        <v>91017</v>
+        <v>91402</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4769,10 +4715,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518357</v>
+        <v>518348</v>
       </c>
       <c r="R36" t="n">
-        <v>6719013</v>
+        <v>6719024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,7 +4750,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4814,12 +4760,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mellan gran och tall, mossmatta.</t>
+          <t>Bland gran och tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4847,45 +4793,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128999291</v>
+        <v>128343538</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>91402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1988</v>
+        <v>256703</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518384</v>
+        <v>518357</v>
       </c>
       <c r="R37" t="n">
-        <v>6719010</v>
+        <v>6719013</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4912,12 +4861,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mellan gran och tall, mossmatta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4926,66 +4890,70 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128999109</v>
+        <v>128394906</v>
       </c>
       <c r="B38" t="n">
-        <v>92834</v>
+        <v>91402</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1435</v>
+        <v>256703</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Finnhyttan, Dlr</t>
+          <t>Finnhyttan, Finnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518364</v>
+        <v>518339</v>
       </c>
       <c r="R38" t="n">
-        <v>6718999</v>
+        <v>6719046</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5009,12 +4977,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5023,50 +5001,51 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130819233</v>
+        <v>130819189</v>
       </c>
       <c r="B39" t="n">
-        <v>92268</v>
+        <v>92329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>6040186</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5079,10 +5058,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518364</v>
+        <v>518368</v>
       </c>
       <c r="R39" t="n">
-        <v>6719063</v>
+        <v>6719049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5154,354 +5133,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>130819210</v>
-      </c>
-      <c r="B40" t="n">
-        <v>91809</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Finnhyttan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>518385</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6719051</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>130819189</v>
-      </c>
-      <c r="B41" t="n">
-        <v>92228</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Finnhyttan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>518368</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6719049</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>130819196</v>
-      </c>
-      <c r="B42" t="n">
-        <v>92107</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>658</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Finnhyttan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>518374</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6719039</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29266-2023 artfynd.xlsx
+++ b/artfynd/A 29266-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130819196</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119542725</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130819210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130819233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999109</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999291</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128395455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128394612</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391555</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128395367</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128395336</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342890</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2100,6 +2165,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128394929</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2231,6 +2301,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391159</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391190</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391285</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391322</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391463</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2866,6 +2961,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391503</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2997,6 +3097,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119391582</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3123,6 +3228,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119392025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3244,6 +3354,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119392079</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3365,6 +3480,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119392138</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3486,6 +3606,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119392358</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3612,6 +3737,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119392415</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3738,6 +3868,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126571260</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3864,6 +3999,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342618</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3976,6 +4116,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342638</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4097,6 +4242,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343148</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4218,6 +4368,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343196</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4339,6 +4494,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343222</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4460,6 +4620,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343284</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4567,6 +4732,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119543003</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4674,6 +4844,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128394409</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4790,6 +4965,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343355</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4906,6 +5086,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343538</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5017,6 +5202,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128394906</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5133,8 +5323,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130819189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>